--- a/data/trans_camb/IP04D$individual-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Habitat-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 16,33</t>
+          <t>-2,26; 15,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 1,42</t>
+          <t>-15,09; 2,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 2,98</t>
+          <t>-13,61; 2,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 17,16</t>
+          <t>-10,82; 18,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 6,43</t>
+          <t>-6,35; 6,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 7,0</t>
+          <t>-10,89; 8,43</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 79,33</t>
+          <t>-8,58; 81,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 7,66</t>
+          <t>-54,05; 11,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 12,31</t>
+          <t>-41,8; 10,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,0; 71,93</t>
+          <t>-34,95; 70,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 27,28</t>
+          <t>-21,03; 25,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 30,2</t>
+          <t>-37,77; 35,52</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 9,39</t>
+          <t>-5,52; 8,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,52; -6,2</t>
+          <t>-18,68; -5,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 8,75</t>
+          <t>-5,02; 8,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,93; -3,0</t>
+          <t>-16,71; -3,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 6,75</t>
+          <t>-3,1; 6,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -6,41</t>
+          <t>-15,87; -6,21</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 37,21</t>
+          <t>-17,34; 34,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,05; -23,4</t>
+          <t>-60,11; -21,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 35,93</t>
+          <t>-16,43; 35,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,51; -10,93</t>
+          <t>-54,22; -12,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 26,7</t>
+          <t>-10,27; 25,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,72; -24,87</t>
+          <t>-52,73; -24,51</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 22,6</t>
+          <t>7,3; 22,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,54; -12,11</t>
+          <t>-23,39; -11,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 15,28</t>
+          <t>-0,55; 15,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,79; -5,62</t>
+          <t>-21,09; -5,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,15</t>
+          <t>5,2; 16,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,54; -11,1</t>
+          <t>-20,74; -10,76</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,39; 128,65</t>
+          <t>27,93; 128,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,5; -64,61</t>
+          <t>-91,91; -65,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 66,45</t>
+          <t>-1,56; 72,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,81; -23,26</t>
+          <t>-70,85; -22,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,95; 75,34</t>
+          <t>19,34; 77,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,96; -48,64</t>
+          <t>-78,27; -46,8</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 2,05</t>
+          <t>-12,9; 2,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 2,71</t>
+          <t>-14,33; 2,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,05; -7,1</t>
+          <t>-22,39; -7,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,62; -6,18</t>
+          <t>-22,24; -5,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,63; -4,45</t>
+          <t>-15,61; -4,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,14; -4,01</t>
+          <t>-16,58; -4,84</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 6,56</t>
+          <t>-33,3; 7,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 8,3</t>
+          <t>-36,56; 6,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,71; -18,5</t>
+          <t>-49,78; -20,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,15; -16,12</t>
+          <t>-49,94; -14,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -12,65</t>
+          <t>-37,04; -11,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,52; -11,17</t>
+          <t>-40,31; -13,4</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,48</t>
+          <t>-0,24; 7,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -8,25</t>
+          <t>-16,09; -8,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,21</t>
+          <t>-6,91; 0,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -6,18</t>
+          <t>-15,14; -6,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,76</t>
+          <t>-2,72; 3,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,56; -8,41</t>
+          <t>-14,37; -8,38</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 28,47</t>
+          <t>-0,83; 28,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,7; -31,48</t>
+          <t>-54,03; -31,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 4,44</t>
+          <t>-20,7; 2,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,99; -20,81</t>
+          <t>-45,05; -19,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 9,69</t>
+          <t>-8,36; 10,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,38; -28,57</t>
+          <t>-46,02; -28,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Habitat-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 15,96</t>
+          <t>-3,3; 15,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 2,04</t>
+          <t>-15,35; 1,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 2,64</t>
+          <t>-14,62; 2,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 18,26</t>
+          <t>-12,23; 16,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 6,17</t>
+          <t>-5,76; 6,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 8,43</t>
+          <t>-10,22; 8,32</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 81,01</t>
+          <t>-12,23; 76,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 11,28</t>
+          <t>-54,76; 10,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 10,53</t>
+          <t>-44,17; 8,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 70,97</t>
+          <t>-38,44; 67,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 25,87</t>
+          <t>-19,16; 26,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 35,52</t>
+          <t>-34,85; 35,49</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 8,58</t>
+          <t>-4,6; 8,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,68; -5,38</t>
+          <t>-19,21; -6,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 8,41</t>
+          <t>-5,01; 9,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,71; -3,43</t>
+          <t>-17,06; -3,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,74</t>
+          <t>-3,04; 7,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,87; -6,21</t>
+          <t>-16,43; -6,26</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 34,96</t>
+          <t>-14,34; 34,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,11; -21,72</t>
+          <t>-61,56; -24,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 35,15</t>
+          <t>-15,78; 39,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,22; -12,85</t>
+          <t>-55,09; -15,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 25,95</t>
+          <t>-10,1; 27,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,73; -24,51</t>
+          <t>-53,14; -23,14</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 22,61</t>
+          <t>6,44; 22,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,39; -11,84</t>
+          <t>-23,77; -11,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 15,88</t>
+          <t>-0,63; 15,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -5,15</t>
+          <t>-22,01; -6,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 16,58</t>
+          <t>5,21; 17,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,74; -10,76</t>
+          <t>-20,37; -10,05</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,93; 128,03</t>
+          <t>23,39; 128,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,91; -65,66</t>
+          <t>-91,33; -65,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 72,81</t>
+          <t>-1,96; 67,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,85; -22,32</t>
+          <t>-73,26; -23,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,34; 77,08</t>
+          <t>19,89; 79,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,27; -46,8</t>
+          <t>-77,54; -44,54</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 2,44</t>
+          <t>-12,93; 2,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 2,1</t>
+          <t>-14,37; 1,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,39; -7,37</t>
+          <t>-21,46; -6,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,24; -5,44</t>
+          <t>-22,47; -5,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,61; -4,05</t>
+          <t>-15,86; -4,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,58; -4,84</t>
+          <t>-15,46; -3,97</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 7,69</t>
+          <t>-33,61; 7,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 6,98</t>
+          <t>-36,96; 6,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,78; -20,24</t>
+          <t>-49,2; -18,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,94; -14,24</t>
+          <t>-50,1; -14,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,04; -11,15</t>
+          <t>-38,32; -13,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,31; -13,4</t>
+          <t>-38,36; -11,41</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,45</t>
+          <t>-0,14; 7,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -8,42</t>
+          <t>-15,94; -8,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,73</t>
+          <t>-6,62; 1,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -6,16</t>
+          <t>-15,12; -5,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,0</t>
+          <t>-2,53; 2,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -8,38</t>
+          <t>-14,51; -8,19</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 28,96</t>
+          <t>-0,58; 28,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,03; -31,62</t>
+          <t>-53,43; -30,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 2,62</t>
+          <t>-19,59; 3,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,05; -19,29</t>
+          <t>-45,81; -18,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 10,43</t>
+          <t>-8,09; 9,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,02; -28,45</t>
+          <t>-46,63; -28,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Habitat-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-5,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>6,73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,95</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,66</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-7,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>-4,0</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 15,67</t>
+          <t>-14,49; 2,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 1,77</t>
+          <t>-11,3; 16,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 2,29</t>
+          <t>-3,0; 16,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 16,39</t>
+          <t>-15,8; 0,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 6,45</t>
+          <t>-5,64; 6,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 8,32</t>
+          <t>-10,41; 5,43</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-19,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-1,99%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>27,46%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-28,38%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-19,27%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,5%</t>
+          <t>-30,1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,86%</t>
+          <t>-14,78%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 76,66</t>
+          <t>-42,17; 12,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 10,73</t>
+          <t>-35,67; 66,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 8,94</t>
+          <t>-10,96; 79,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 67,73</t>
+          <t>-53,58; 6,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 26,62</t>
+          <t>-19,09; 27,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 35,49</t>
+          <t>-36,17; 23,23</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-10,67</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>2,08</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-12,8</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,12</t>
+          <t>-11,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,31</t>
+          <t>-11,26</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 8,77</t>
+          <t>-5,0; 8,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,21; -6,04</t>
+          <t>-17,08; -3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 9,69</t>
+          <t>-5,29; 9,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,06; -3,89</t>
+          <t>-18,74; -4,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 7,11</t>
+          <t>-3,41; 6,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,43; -6,26</t>
+          <t>-16,0; -6,43</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-38,24%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>7,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-44,68%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-36,3%</t>
+          <t>-41,69%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-40,01%</t>
+          <t>-39,84%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 34,71</t>
+          <t>-16,48; 35,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,56; -24,19</t>
+          <t>-55,93; -12,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 39,63</t>
+          <t>-16,71; 37,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,09; -15,27</t>
+          <t>-58,9; -18,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 27,8</t>
+          <t>-11,19; 26,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,14; -23,14</t>
+          <t>-52,61; -25,19</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,42</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-13,64</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>14,51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-17,43</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,42</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-14,29</t>
+          <t>-16,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-15,99</t>
+          <t>-15,18</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 22,61</t>
+          <t>-1,06; 15,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,77; -11,88</t>
+          <t>-21,1; -4,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 15,72</t>
+          <t>6,88; 22,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,01; -6,0</t>
+          <t>-22,74; -11,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 17,04</t>
+          <t>4,97; 16,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,37; -10,05</t>
+          <t>-19,76; -9,93</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28,05%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-51,52%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>67,56%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-81,18%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>28,05%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-54,01%</t>
+          <t>-78,45%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-66,52%</t>
+          <t>-63,11%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,39; 128,17</t>
+          <t>-3,32; 66,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,33; -65,51</t>
+          <t>-69,74; -17,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 67,89</t>
+          <t>28,39; 128,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,26; -23,15</t>
+          <t>-88,99; -59,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,89; 79,85</t>
+          <t>17,95; 75,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,54; -44,54</t>
+          <t>-75,32; -44,11</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-14,53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-14,55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-5,16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-6,03</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-14,53</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-14,64</t>
+          <t>-6,42</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,37</t>
+          <t>-10,48</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 2,48</t>
+          <t>-23,05; -7,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 1,85</t>
+          <t>-22,47; -6,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,46; -6,53</t>
+          <t>-13,25; 2,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,47; -5,87</t>
+          <t>-14,34; 2,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -4,81</t>
+          <t>-15,63; -4,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -3,97</t>
+          <t>-16,14; -3,95</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-35,02%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-35,08%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-14,62%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-17,09%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-35,02%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-35,29%</t>
+          <t>-18,2%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-27,02%</t>
+          <t>-27,31%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 7,87</t>
+          <t>-48,71; -18,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 6,12</t>
+          <t>-49,66; -15,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,2; -18,12</t>
+          <t>-33,86; 6,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,1; -14,83</t>
+          <t>-36,53; 7,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,32; -13,24</t>
+          <t>-37,8; -12,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,36; -11,41</t>
+          <t>-39,48; -10,9</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,99</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-11,06</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>3,59</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-12,07</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-11,08</t>
+          <t>-11,22</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-11,48</t>
+          <t>-11,1</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,37</t>
+          <t>-6,67; 1,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -8,09</t>
+          <t>-15,22; -6,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 1,11</t>
+          <t>-0,71; 7,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -5,85</t>
+          <t>-14,84; -7,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,63</t>
+          <t>-2,75; 2,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -8,19</t>
+          <t>-14,19; -8,1</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-9,45%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-34,95%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>12,71%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-42,77%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-9,45%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-35,03%</t>
+          <t>-39,77%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-38,29%</t>
+          <t>-37,01%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 28,14</t>
+          <t>-19,87; 4,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,43; -30,32</t>
+          <t>-46,0; -21,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 3,8</t>
+          <t>-2,4; 28,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -18,96</t>
+          <t>-49,41; -28,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 9,33</t>
+          <t>-8,71; 9,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,63; -28,51</t>
+          <t>-44,93; -27,99</t>
         </is>
       </c>
     </row>
